--- a/backend/data/financials_by_company/002049.SZ.xlsx
+++ b/backend/data/financials_by_company/002049.SZ.xlsx
@@ -4030,202 +4030,202 @@
       </c>
       <c r="DS1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FD1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FE1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FD1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FE1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FF1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="FG1" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Tianchi  Li', 'age': 57, 'title': 'President &amp; Director', 'yearBorn': 1968, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Qiuping  Yang CPA', 'age': 51, 'title': 'CFO &amp; Financial Director', 'yearBorn': 1974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaodan  Tong', 'age': 52, 'title': 'Board Secretary', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chao  Yue', 'age': 42, 'title': 'Vice President', 'yearBorn': 1983, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ying Bin  Zhai', 'age': 57, 'title': 'Vice President', 'yearBorn': 1968, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dianhong  Zhang', 'title': 'Head of Accounting Organization &amp; Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4324,7 +4324,7 @@
         <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>1780531200</v>
+        <v>1782864000</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -4338,37 +4338,37 @@
         <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>80.39</v>
+        <v>83.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>79.90000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>79.98</v>
+        <v>81.12</v>
       </c>
       <c r="AB2" t="n">
-        <v>82.48</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>80.39</v>
+        <v>83.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>79.90000000000001</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>79.98</v>
+        <v>81.12</v>
       </c>
       <c r="AF2" t="n">
-        <v>82.48</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="AI2" t="n">
-        <v>1750896000</v>
+        <v>1782777600</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.1071</v>
@@ -4377,34 +4377,34 @@
         <v>0.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.425</v>
+        <v>0.412</v>
       </c>
       <c r="AM2" t="n">
-        <v>41.816326</v>
+        <v>41.714287</v>
       </c>
       <c r="AN2" t="n">
-        <v>28.859156</v>
+        <v>28.788734</v>
       </c>
       <c r="AO2" t="n">
-        <v>43474278</v>
+        <v>38145194</v>
       </c>
       <c r="AP2" t="n">
-        <v>43474278</v>
+        <v>38145194</v>
       </c>
       <c r="AQ2" t="n">
-        <v>29658024</v>
+        <v>35894941</v>
       </c>
       <c r="AR2" t="n">
-        <v>31263216</v>
+        <v>49288646</v>
       </c>
       <c r="AS2" t="n">
-        <v>31263216</v>
+        <v>49288646</v>
       </c>
       <c r="AT2" t="n">
-        <v>81.93000000000001</v>
+        <v>81.73</v>
       </c>
       <c r="AU2" t="n">
-        <v>81.95</v>
+        <v>81.75</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4413,13 +4413,13 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>69635530752</v>
+        <v>69465718784</v>
       </c>
       <c r="AY2" t="n">
-        <v>68301620001</v>
+        <v>73416484317</v>
       </c>
       <c r="AZ2" t="n">
-        <v>61.52</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="BA2" t="n">
         <v>94.83</v>
@@ -4431,19 +4431,19 @@
         <v>1.111113</v>
       </c>
       <c r="BD2" t="n">
-        <v>10.520725</v>
+        <v>10.4950695</v>
       </c>
       <c r="BE2" t="n">
-        <v>76.43000000000001</v>
+        <v>78.8796</v>
       </c>
       <c r="BF2" t="n">
-        <v>78.07545</v>
+        <v>78.3496</v>
       </c>
       <c r="BG2" t="n">
         <v>0.31</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0038562012</v>
+        <v>0.003710353</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
@@ -4454,31 +4454,31 @@
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>66995879936</v>
+        <v>66827853824</v>
       </c>
       <c r="BL2" t="n">
         <v>0.24961</v>
       </c>
       <c r="BM2" t="n">
-        <v>611716065</v>
+        <v>611766474</v>
       </c>
       <c r="BN2" t="n">
-        <v>849628312</v>
+        <v>849629544</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.30278</v>
+        <v>0.3026</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.114580005</v>
+        <v>0.103319995</v>
       </c>
       <c r="BQ2" t="n">
-        <v>849628312</v>
+        <v>849629544</v>
       </c>
       <c r="BR2" t="n">
         <v>16.783</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.883513</v>
+        <v>4.8715963</v>
       </c>
       <c r="BT2" t="n">
         <v>1767139200</v>
@@ -4513,22 +4513,22 @@
         <v>1661299200</v>
       </c>
       <c r="CD2" t="n">
-        <v>10.122</v>
+        <v>10.097</v>
       </c>
       <c r="CE2" t="n">
-        <v>39.452</v>
+        <v>39.353</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.28316045</v>
+        <v>0.2907462</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="CI2" t="n">
-        <v>1750896000</v>
+        <v>1782777600</v>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>81.95999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="CL2" t="n">
         <v>120.52</v>
@@ -4655,147 +4655,147 @@
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DT2" t="b">
+          <t>Unigroup Guoxin Microelectronics Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>-1.7900009</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>81.12 - 84.4</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>35894941</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.27730042</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>64.01 - 94.83</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>-13.07</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-0.13782558</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>29.074621</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>1745924340</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1745924340</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1746774000</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1746774000</v>
+      </c>
+      <c r="EH2" t="b">
         <v>0</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="EI2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>UNIGROUP GUOXIN MICROELECTRONIC</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EM2" t="n">
+        <v>1783062246</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>finmb_22277502</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="ER2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="ET2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>-2.1424305</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>81.76000000000001</v>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EX2" t="n">
+        <v>2.8804016</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>0.03651643</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>3.4104004</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>0.043527987</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FF2" t="n">
         <v>1118021400000</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1.5699997</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>79.98 - 82.48</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>29658024</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>20.439999</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.33224964</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>61.52 - 94.83</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>-12.870003</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.13571657</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>28.316044</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1745924340</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1745924340</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1746774000</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1746774000</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>UNIGROUP GUOXIN MICROELECTRONIC</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>Unigroup Guoxin Microelectronics Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EP2" t="n">
-        <v>1782111855</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1.9529787</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>81.95999999999999</v>
-      </c>
-      <c r="ES2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>finmb_22277502</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EW2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>5.529999</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>0.07235377</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>3.884552</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>0.049753822</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FF2" t="b">
-        <v>0</v>
       </c>
       <c r="FG2" t="inlineStr"/>
     </row>
